--- a/table/Datas/#ArcheryRange.xlsx
+++ b/table/Datas/#ArcheryRange.xlsx
@@ -533,7 +533,7 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7">
@@ -567,7 +567,7 @@
         <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>225</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8">
@@ -584,7 +584,7 @@
         <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         <v>65</v>
       </c>
       <c r="F9" t="n">
-        <v>275</v>
+        <v>550</v>
       </c>
     </row>
     <row r="10">
@@ -618,7 +618,7 @@
         <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryRange.xlsx
+++ b/table/Datas/#ArcheryRange.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,16 @@
           <t>exposure_ticks</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>lateral_span_m</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lateral_period_s</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,6 +489,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -486,6 +506,8 @@
           <t>##group</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -516,6 +538,16 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>exposure_ticks</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>lateral_span_m</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>lateral_period_s</t>
         </is>
       </c>
     </row>
@@ -535,6 +567,12 @@
       <c r="F5" t="n">
         <v>400</v>
       </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -552,6 +590,12 @@
       <c r="F6" t="n">
         <v>400</v>
       </c>
+      <c r="G6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -569,6 +613,12 @@
       <c r="F7" t="n">
         <v>450</v>
       </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -586,6 +636,12 @@
       <c r="F8" t="n">
         <v>500</v>
       </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -603,6 +659,12 @@
       <c r="F9" t="n">
         <v>550</v>
       </c>
+      <c r="G9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -619,6 +681,12 @@
       </c>
       <c r="F10" t="n">
         <v>600</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryRange.xlsx
+++ b/table/Datas/#ArcheryRange.xlsx
@@ -506,8 +506,6 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -568,7 +566,7 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -591,7 +589,7 @@
         <v>400</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -614,7 +612,7 @@
         <v>450</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>3</v>
@@ -637,7 +635,7 @@
         <v>500</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>3.5</v>
@@ -660,7 +658,7 @@
         <v>550</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -683,7 +681,7 @@
         <v>600</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>4.5</v>

--- a/table/Datas/#ArcheryRange.xlsx
+++ b/table/Datas/#ArcheryRange.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>lateral_period_s</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>face_radius_m</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +504,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -546,6 +556,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>lateral_period_s</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>face_radius_m</t>
         </is>
       </c>
     </row>
@@ -571,6 +586,9 @@
       <c r="H5" t="n">
         <v>3</v>
       </c>
+      <c r="I5" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -594,6 +612,9 @@
       <c r="H6" t="n">
         <v>3</v>
       </c>
+      <c r="I6" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -617,6 +638,9 @@
       <c r="H7" t="n">
         <v>3</v>
       </c>
+      <c r="I7" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -640,6 +664,9 @@
       <c r="H8" t="n">
         <v>3.5</v>
       </c>
+      <c r="I8" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -663,6 +690,9 @@
       <c r="H9" t="n">
         <v>4</v>
       </c>
+      <c r="I9" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -685,6 +715,9 @@
       </c>
       <c r="H10" t="n">
         <v>4.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryRange.xlsx
+++ b/table/Datas/#ArcheryRange.xlsx
@@ -580,8 +580,8 @@
       <c r="F5" t="n">
         <v>400</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
+      <c r="G5">
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -606,8 +606,8 @@
       <c r="F6" t="n">
         <v>400</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
+      <c r="G6">
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -632,8 +632,8 @@
       <c r="F7" t="n">
         <v>450</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
+      <c r="G7">
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>3</v>
@@ -658,8 +658,8 @@
       <c r="F8" t="n">
         <v>500</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
+      <c r="G8">
+        <v>3.5</v>
       </c>
       <c r="H8" t="n">
         <v>3.5</v>
@@ -684,8 +684,8 @@
       <c r="F9" t="n">
         <v>550</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
+      <c r="G9">
+        <v>4</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -710,8 +710,8 @@
       <c r="F10" t="n">
         <v>600</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
+      <c r="G10">
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>4.5</v>

--- a/table/Datas/#ArcheryRange.xlsx
+++ b/table/Datas/#ArcheryRange.xlsx
@@ -582,6 +582,7 @@
       </c>
       <c r="G5">
         <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -608,6 +609,7 @@
       </c>
       <c r="G6">
         <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -634,6 +636,7 @@
       </c>
       <c r="G7">
         <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
         <v>3</v>
@@ -660,6 +663,7 @@
       </c>
       <c r="G8">
         <v>3.5</v>
+        <v>1.87</v>
       </c>
       <c r="H8" t="n">
         <v>3.5</v>
@@ -686,6 +690,7 @@
       </c>
       <c r="G9">
         <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -712,6 +717,7 @@
       </c>
       <c r="G10">
         <v>5</v>
+        <v>1.83</v>
       </c>
       <c r="H10" t="n">
         <v>4.5</v>

--- a/table/Datas/#ArcheryRange.xlsx
+++ b/table/Datas/#ArcheryRange.xlsx
@@ -577,11 +577,10 @@
       <c r="E5" t="n">
         <v>12</v>
       </c>
-      <c r="F5" t="n">
-        <v>400</v>
+      <c r="F5">
+        <v>580</v>
       </c>
       <c r="G5">
-        <v>2</v>
         <v>3</v>
       </c>
       <c r="H5" t="n">
@@ -604,11 +603,10 @@
       <c r="E6" t="n">
         <v>20</v>
       </c>
-      <c r="F6" t="n">
-        <v>400</v>
+      <c r="F6">
+        <v>580</v>
       </c>
       <c r="G6">
-        <v>2.5</v>
         <v>2.7</v>
       </c>
       <c r="H6" t="n">
@@ -631,11 +629,10 @@
       <c r="E7" t="n">
         <v>30</v>
       </c>
-      <c r="F7" t="n">
-        <v>450</v>
+      <c r="F7">
+        <v>650</v>
       </c>
       <c r="G7">
-        <v>3</v>
         <v>1.8</v>
       </c>
       <c r="H7" t="n">
@@ -658,11 +655,10 @@
       <c r="E8" t="n">
         <v>45</v>
       </c>
-      <c r="F8" t="n">
-        <v>500</v>
+      <c r="F8">
+        <v>725</v>
       </c>
       <c r="G8">
-        <v>3.5</v>
         <v>1.87</v>
       </c>
       <c r="H8" t="n">
@@ -685,11 +681,10 @@
       <c r="E9" t="n">
         <v>65</v>
       </c>
-      <c r="F9" t="n">
-        <v>550</v>
+      <c r="F9">
+        <v>800</v>
       </c>
       <c r="G9">
-        <v>4</v>
         <v>1.85</v>
       </c>
       <c r="H9" t="n">
@@ -712,11 +707,10 @@
       <c r="E10" t="n">
         <v>90</v>
       </c>
-      <c r="F10" t="n">
-        <v>600</v>
+      <c r="F10">
+        <v>865</v>
       </c>
       <c r="G10">
-        <v>5</v>
         <v>1.83</v>
       </c>
       <c r="H10" t="n">

--- a/table/Datas/#ArcheryRange.xlsx
+++ b/table/Datas/#ArcheryRange.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,16 @@
           <t>face_radius_m</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>wind_mps2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>points_multiplier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +519,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -563,6 +583,16 @@
           <t>face_radius_m</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>wind_mps2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>points_multiplier</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -577,10 +607,10 @@
       <c r="E5" t="n">
         <v>12</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>580</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
@@ -588,6 +618,12 @@
       </c>
       <c r="I5" t="n">
         <v>0.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -603,10 +639,10 @@
       <c r="E6" t="n">
         <v>20</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>580</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>2.7</v>
       </c>
       <c r="H6" t="n">
@@ -614,6 +650,12 @@
       </c>
       <c r="I6" t="n">
         <v>0.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -629,10 +671,10 @@
       <c r="E7" t="n">
         <v>30</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>650</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>1.8</v>
       </c>
       <c r="H7" t="n">
@@ -640,6 +682,12 @@
       </c>
       <c r="I7" t="n">
         <v>0.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -655,10 +703,10 @@
       <c r="E8" t="n">
         <v>45</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>725</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>1.87</v>
       </c>
       <c r="H8" t="n">
@@ -666,6 +714,12 @@
       </c>
       <c r="I8" t="n">
         <v>0.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -681,10 +735,10 @@
       <c r="E9" t="n">
         <v>65</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>800</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>1.85</v>
       </c>
       <c r="H9" t="n">
@@ -692,6 +746,12 @@
       </c>
       <c r="I9" t="n">
         <v>0.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -707,10 +767,10 @@
       <c r="E10" t="n">
         <v>90</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>865</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1.83</v>
       </c>
       <c r="H10" t="n">
@@ -718,6 +778,396 @@
       </c>
       <c r="I10" t="n">
         <v>0.61</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>101</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>250</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>102</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" t="n">
+        <v>250</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>103</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>104</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" t="n">
+        <v>250</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>105</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" t="n">
+        <v>250</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>106</v>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>30</v>
+      </c>
+      <c r="F16" t="n">
+        <v>250</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>107</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" t="n">
+        <v>250</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>108</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>65</v>
+      </c>
+      <c r="F18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>109</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" t="n">
+        <v>250</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>12</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>110</v>
+      </c>
+      <c r="C20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" t="n">
+        <v>250</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>111</v>
+      </c>
+      <c r="C21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>45</v>
+      </c>
+      <c r="F21" t="n">
+        <v>250</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>112</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>45</v>
+      </c>
+      <c r="F22" t="n">
+        <v>250</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>12</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryRange.xlsx
+++ b/table/Datas/#ArcheryRange.xlsx
@@ -876,7 +876,7 @@
         <v>0.3</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -899,7 +899,7 @@
         <v>250</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="H14" t="n">
         <v>3.2</v>
@@ -972,7 +972,7 @@
         <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>-18</v>
+        <v>-3</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -995,7 +995,7 @@
         <v>250</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
@@ -1059,7 +1059,7 @@
         <v>250</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>2.8</v>
@@ -1068,7 +1068,7 @@
         <v>0.3</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1091,7 +1091,7 @@
         <v>250</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="H20" t="n">
         <v>2.2</v>
@@ -1132,7 +1132,7 @@
         <v>0.4</v>
       </c>
       <c r="J21" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>250</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1164,7 +1164,7 @@
         <v>0.4</v>
       </c>
       <c r="J22" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>2</v>

--- a/table/Datas/#ArcheryRange.xlsx
+++ b/table/Datas/#ArcheryRange.xlsx
@@ -876,7 +876,7 @@
         <v>0.3</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -899,7 +899,7 @@
         <v>250</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="n">
         <v>3.2</v>
@@ -972,7 +972,7 @@
         <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -995,7 +995,7 @@
         <v>250</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
@@ -1059,7 +1059,7 @@
         <v>250</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H19" t="n">
         <v>2.8</v>
@@ -1068,7 +1068,7 @@
         <v>0.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1091,7 +1091,7 @@
         <v>250</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>2.2</v>
@@ -1132,7 +1132,7 @@
         <v>0.4</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>250</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1164,7 +1164,7 @@
         <v>0.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
         <v>2</v>

--- a/table/Datas/#ArcheryRange.xlsx
+++ b/table/Datas/#ArcheryRange.xlsx
@@ -800,7 +800,7 @@
         <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -832,7 +832,7 @@
         <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -864,7 +864,7 @@
         <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -896,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G14" t="n">
         <v>1.7</v>
@@ -928,7 +928,7 @@
         <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
         <v>30</v>
       </c>
       <c r="F16" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
@@ -1024,7 +1024,7 @@
         <v>65</v>
       </c>
       <c r="F18" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1056,7 +1056,7 @@
         <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G19" t="n">
         <v>1.3</v>
@@ -1088,7 +1088,7 @@
         <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -1120,7 +1120,7 @@
         <v>45</v>
       </c>
       <c r="F21" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>45</v>
       </c>
       <c r="F22" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G22" t="n">
         <v>1.3</v>

--- a/table/Datas/#ArcheryRange.xlsx
+++ b/table/Datas/#ArcheryRange.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,10 +596,10 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -608,16 +608,16 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>580</v>
+        <v>375</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -628,10 +628,10 @@
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>580</v>
+        <v>375</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0.3</v>
@@ -660,31 +660,31 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>650</v>
+        <v>375</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0.3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -692,28 +692,28 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>725</v>
+        <v>375</v>
       </c>
       <c r="G8" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -724,28 +724,28 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>800</v>
+        <v>375</v>
       </c>
       <c r="G9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.18</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -756,31 +756,31 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>865</v>
+        <v>375</v>
       </c>
       <c r="G10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -788,25 +788,25 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
         <v>375</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>0.3</v>
@@ -820,16 +820,16 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
         <v>375</v>
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -852,25 +852,25 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F13" t="n">
         <v>375</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I13" t="n">
         <v>0.3</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
@@ -899,13 +899,13 @@
         <v>375</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -916,16 +916,16 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F15" t="n">
         <v>375</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -948,225 +948,33 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F16" t="n">
         <v>375</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="n">
-        <v>107</v>
-      </c>
-      <c r="C17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>20</v>
-      </c>
-      <c r="F17" t="n">
-        <v>375</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="n">
-        <v>108</v>
-      </c>
-      <c r="C18" t="n">
-        <v>7</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" t="n">
-        <v>65</v>
-      </c>
-      <c r="F18" t="n">
-        <v>375</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="n">
-        <v>109</v>
-      </c>
-      <c r="C19" t="n">
-        <v>7</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>30</v>
-      </c>
-      <c r="F19" t="n">
-        <v>375</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="n">
-        <v>110</v>
-      </c>
-      <c r="C20" t="n">
-        <v>7</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>20</v>
-      </c>
-      <c r="F20" t="n">
-        <v>375</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="n">
-        <v>111</v>
-      </c>
-      <c r="C21" t="n">
-        <v>7</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>45</v>
-      </c>
-      <c r="F21" t="n">
-        <v>375</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="n">
-        <v>112</v>
-      </c>
-      <c r="C22" t="n">
-        <v>7</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" t="n">
-        <v>45</v>
-      </c>
-      <c r="F22" t="n">
-        <v>375</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" t="n">
         <v>2</v>
       </c>
     </row>
